--- a/SuppXLS/Scen_UC_RNWHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_RNWHEAT_20_50.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE510AAF-F712-428F-BB28-904E713C4CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4E693-4763-4C53-BAA1-298F0C91E7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="432" windowWidth="21600" windowHeight="11232" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
     <sheet name="RNWHEAT_20_50" sheetId="1" r:id="rId1"/>
@@ -98,13 +98,13 @@
     <t>RNWHEAT</t>
   </si>
   <si>
-    <t>HEAT</t>
-  </si>
-  <si>
     <t>UC_RNWHEAT_ELC_20_50</t>
   </si>
   <si>
     <t>Minimum RNWHEAT penetration</t>
+  </si>
+  <si>
+    <t>MANHEAT</t>
   </si>
 </sst>
 </file>
@@ -686,13 +686,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I6">
         <v>2030</v>
@@ -713,18 +713,18 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I7">
         <v>2050</v>
@@ -745,7 +745,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_UC_RNWHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_RNWHEAT_20_50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4E693-4763-4C53-BAA1-298F0C91E7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599464D7-BB6F-421A-B4FC-558494AF2D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>MANHEAT</t>
+  </si>
+  <si>
+    <t>HEAT</t>
   </si>
 </sst>
 </file>
@@ -689,6 +692,9 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="G6" t="s">
@@ -721,6 +727,9 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
         <v>19</v>
       </c>
       <c r="G7" t="s">

--- a/SuppXLS/Scen_UC_RNWHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_RNWHEAT_20_50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599464D7-BB6F-421A-B4FC-558494AF2D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097DB3B3-59A5-453F-A8F4-CB408332250F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>HEAT</t>
+  </si>
+  <si>
+    <t>UC_COMPRD</t>
   </si>
 </sst>
 </file>
@@ -700,6 +703,9 @@
       <c r="G6" t="s">
         <v>22</v>
       </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
       <c r="I6">
         <v>2030</v>
       </c>
@@ -734,6 +740,9 @@
       </c>
       <c r="G7" t="s">
         <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
       </c>
       <c r="I7">
         <v>2050</v>
